--- a/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
+++ b/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA ANALITICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26C36DA-4C4E-4A11-8BF0-9EF98B904402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A26C36DA-4C4E-4A11-8BF0-9EF98B904402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87DE135B-172D-46D6-99CA-DCE895BF67C3}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="51">
   <si>
     <t>jingshuo_wang</t>
   </si>
@@ -174,9 +174,6 @@
     <t>Luis_Moliner</t>
   </si>
   <si>
-    <t>Alejandro_Garcia_Gumiel</t>
-  </si>
-  <si>
     <t>Noah_Ojo_Barranco</t>
   </si>
   <si>
@@ -323,8 +320,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:O229" totalsRowShown="0">
-  <autoFilter ref="A1:O229" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:O221" totalsRowShown="0">
+  <autoFilter ref="A1:O221" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="3"/>
@@ -643,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -5084,7 +5081,7 @@
         <v>34</v>
       </c>
       <c r="H204" s="5">
-        <v>227.23962929999999</v>
+        <v>236.75833349999999</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
@@ -5099,7 +5096,7 @@
         <v>35</v>
       </c>
       <c r="H205" s="6">
-        <v>227.9269773</v>
+        <v>263.56862719999998</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
@@ -5114,7 +5111,7 @@
         <v>3</v>
       </c>
       <c r="H206" s="5">
-        <v>216.18608080000001</v>
+        <v>271.24947850000001</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
@@ -5126,10 +5123,10 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H207" s="6">
-        <v>140.8273495</v>
+        <v>192.74452819999999</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
@@ -5144,7 +5141,7 @@
         <v>2</v>
       </c>
       <c r="H208" s="5">
-        <v>193.9871292</v>
+        <v>239.46257309999999</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
@@ -5156,10 +5153,10 @@
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H209" s="6">
-        <v>141.35643469999999</v>
+        <v>164.13982559999999</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
@@ -5174,7 +5171,7 @@
         <v>34</v>
       </c>
       <c r="H210" s="5">
-        <v>236.75833349999999</v>
+        <v>195.5292068</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
@@ -5189,7 +5186,7 @@
         <v>35</v>
       </c>
       <c r="H211" s="6">
-        <v>263.56862719999998</v>
+        <v>179.66785719999999</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
@@ -5204,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="H212" s="5">
-        <v>271.24947850000001</v>
+        <v>178.1463938</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
@@ -5219,7 +5216,7 @@
         <v>5</v>
       </c>
       <c r="H213" s="6">
-        <v>192.74452819999999</v>
+        <v>151.06453780000001</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
@@ -5234,7 +5231,7 @@
         <v>2</v>
       </c>
       <c r="H214" s="5">
-        <v>239.46257309999999</v>
+        <v>169.51222519999999</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
@@ -5249,216 +5246,96 @@
         <v>4</v>
       </c>
       <c r="H215" s="6">
-        <v>164.13982559999999</v>
+        <v>156.43160549999999</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B216" s="1">
         <v>46247</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H216" s="5">
-        <v>195.5292068</v>
+        <v>384.39131099999997</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B217" s="1">
         <v>46247</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H217" s="6">
-        <v>179.66785719999999</v>
+        <v>374.53152899999998</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B218" s="1">
         <v>46247</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="5" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H218" s="5">
-        <v>178.1463938</v>
+        <v>610.31778589999999</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B219" s="1">
         <v>46247</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="6" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H219" s="6">
-        <v>151.06453780000001</v>
+        <v>756.06069579999996</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B220" s="1">
         <v>46247</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="5" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H220" s="5">
-        <v>169.51222519999999</v>
+        <v>396.74451349999998</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B221" s="1">
         <v>46247</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="6" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H221" s="6">
-        <v>156.43160549999999</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A222" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B222" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C222" s="2"/>
-      <c r="D222" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H222" s="5">
-        <v>384.39131099999997</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A223" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B223" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C223" s="2"/>
-      <c r="D223" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H223" s="6">
-        <v>374.53152899999998</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A224" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B224" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C224" s="2"/>
-      <c r="D224" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H224" s="5">
-        <v>258.39252909999999</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A225" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B225" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C225" s="2"/>
-      <c r="D225" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H225" s="6">
-        <v>262.27258410000002</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B226" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C226" s="2"/>
-      <c r="D226" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H226" s="5">
-        <v>610.31778589999999</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B227" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H227" s="6">
-        <v>756.06069579999996</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B228" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H228" s="5">
-        <v>396.74451349999998</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B229" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H229" s="6">
         <v>366.27056010000001</v>
       </c>
     </row>
